--- a/dados/gerencial/consolidado_gerencial_2020.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2020.xlsx
@@ -494,13 +494,13 @@
         <v>157</v>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E4" t="n">
-        <v>708669.64</v>
+        <v>708940.12</v>
       </c>
       <c r="F4" t="n">
-        <v>470093.79</v>
+        <v>467941.42</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>43873</v>
@@ -522,13 +522,13 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>82973.83</v>
+        <v>83084.02</v>
       </c>
       <c r="F5" t="n">
-        <v>57840.84</v>
+        <v>57596.07</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>43871</v>
+        <v>43872</v>
       </c>
     </row>
     <row r="6">
@@ -544,16 +544,16 @@
         <v>142</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E6" t="n">
-        <v>631955.79</v>
+        <v>631941.53</v>
       </c>
       <c r="F6" t="n">
-        <v>408833.42</v>
+        <v>409381.17</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43903</v>
+        <v>43902</v>
       </c>
     </row>
     <row r="7">
@@ -572,13 +572,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>95281.53</v>
+        <v>95837.88</v>
       </c>
       <c r="F7" t="n">
-        <v>64974.56</v>
+        <v>64931.39</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>43899</v>
+        <v>43902</v>
       </c>
     </row>
     <row r="8">
@@ -594,16 +594,16 @@
         <v>123</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>563400.92</v>
+        <v>562109.42</v>
       </c>
       <c r="F8" t="n">
-        <v>368613.56</v>
+        <v>370169.14</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>43931</v>
+        <v>43935</v>
       </c>
     </row>
     <row r="9">
@@ -622,13 +622,13 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>94951.74000000001</v>
+        <v>95619.60000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>65762.44</v>
+        <v>66711.3</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>43930</v>
+        <v>43936</v>
       </c>
     </row>
     <row r="10">
@@ -644,16 +644,16 @@
         <v>102</v>
       </c>
       <c r="D10" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" t="n">
-        <v>475880.63</v>
+        <v>477101.2</v>
       </c>
       <c r="F10" t="n">
-        <v>302665.93</v>
+        <v>303545.72</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>43964</v>
+        <v>43965</v>
       </c>
     </row>
     <row r="11">
@@ -672,13 +672,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>95635.09</v>
+        <v>94181.78999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>66768.19</v>
+        <v>63951.86</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>43966</v>
+        <v>43964</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>412336.48</v>
+        <v>411682.97</v>
       </c>
       <c r="F12" t="n">
-        <v>255519.87</v>
+        <v>254413.15</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>43992</v>
+        <v>43997</v>
       </c>
     </row>
     <row r="13">
@@ -722,13 +722,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>95064.78</v>
+        <v>95488.22</v>
       </c>
       <c r="F13" t="n">
-        <v>66957.39</v>
+        <v>65276.37</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>43997</v>
+        <v>43991</v>
       </c>
     </row>
     <row r="14">
@@ -747,13 +747,13 @@
         <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>411316.67</v>
+        <v>409874.95</v>
       </c>
       <c r="F14" t="n">
-        <v>263078</v>
+        <v>260961.29</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44021</v>
+        <v>44025</v>
       </c>
     </row>
     <row r="15">
@@ -772,13 +772,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>96896.69</v>
+        <v>96528.49000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>66972.78</v>
+        <v>65444.84</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>44021</v>
+        <v>44020</v>
       </c>
     </row>
     <row r="16">
@@ -791,16 +791,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
         <v>38</v>
       </c>
       <c r="E16" t="n">
-        <v>469717.12</v>
+        <v>471913.4</v>
       </c>
       <c r="F16" t="n">
-        <v>315654.91</v>
+        <v>317937.1</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>44053</v>
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>96968.62</v>
+        <v>95517.77</v>
       </c>
       <c r="F17" t="n">
-        <v>67131.14</v>
+        <v>65970.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>44056</v>
+        <v>44054</v>
       </c>
     </row>
     <row r="18">
@@ -844,16 +844,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>497676.55</v>
+        <v>496723.19</v>
       </c>
       <c r="F18" t="n">
-        <v>335416.84</v>
+        <v>334860.85</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>44085</v>
+        <v>44088</v>
       </c>
     </row>
     <row r="19">
@@ -872,13 +872,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>115484.14</v>
+        <v>117295.83</v>
       </c>
       <c r="F19" t="n">
-        <v>80653.95</v>
+        <v>80546.27</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>44088</v>
+        <v>44084</v>
       </c>
     </row>
     <row r="20">
@@ -894,16 +894,16 @@
         <v>121</v>
       </c>
       <c r="D20" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E20" t="n">
-        <v>562198.75</v>
+        <v>560423.99</v>
       </c>
       <c r="F20" t="n">
-        <v>372672.29</v>
+        <v>375927.99</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>44113</v>
+        <v>44112</v>
       </c>
     </row>
     <row r="21">
@@ -922,13 +922,13 @@
         <v>6</v>
       </c>
       <c r="E21" t="n">
-        <v>161090.82</v>
+        <v>162261.69</v>
       </c>
       <c r="F21" t="n">
-        <v>103613.01</v>
+        <v>104510.82</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>44119</v>
+        <v>44116</v>
       </c>
     </row>
     <row r="22">
@@ -947,13 +947,13 @@
         <v>50</v>
       </c>
       <c r="E22" t="n">
-        <v>590682.61</v>
+        <v>590826.37</v>
       </c>
       <c r="F22" t="n">
-        <v>406858.81</v>
+        <v>406874.68</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>44151</v>
+        <v>44147</v>
       </c>
     </row>
     <row r="23">
@@ -972,10 +972,10 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>191342.1</v>
+        <v>191062.26</v>
       </c>
       <c r="F23" t="n">
-        <v>125588.22</v>
+        <v>124433.78</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>44144</v>
@@ -997,10 +997,10 @@
         <v>43</v>
       </c>
       <c r="E24" t="n">
-        <v>606382.76</v>
+        <v>606658.01</v>
       </c>
       <c r="F24" t="n">
-        <v>405382.01</v>
+        <v>409241.19</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>44179</v>
@@ -1019,13 +1019,13 @@
         <v>45</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>196877.74</v>
+        <v>196227.77</v>
       </c>
       <c r="F25" t="n">
-        <v>126963.97</v>
+        <v>126412.52</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>44179</v>
@@ -1047,13 +1047,13 @@
         <v>48</v>
       </c>
       <c r="E26" t="n">
-        <v>592931.55</v>
+        <v>593669.45</v>
       </c>
       <c r="F26" t="n">
-        <v>406165.05</v>
+        <v>407254.03</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>44209</v>
+        <v>44211</v>
       </c>
     </row>
     <row r="27">
@@ -1072,10 +1072,10 @@
         <v>5</v>
       </c>
       <c r="E27" t="n">
-        <v>217657.11</v>
+        <v>216570.73</v>
       </c>
       <c r="F27" t="n">
-        <v>141925.25</v>
+        <v>142949.75</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>44207</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E28" t="n">
-        <v>8063373.66</v>
+        <v>8061540.65</v>
       </c>
       <c r="F28" t="n">
-        <v>5346106.22</v>
+        <v>5347243</v>
       </c>
     </row>
   </sheetData>
